--- a/tools/importer/reports/import-about-us.report.xlsx
+++ b/tools/importer/reports/import-about-us.report.xlsx
@@ -37,7 +37,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-09-03T01:25:30.860Z</t>
+    <t>2026-09-03T05:47:53.973Z</t>
   </si>
   <si>
     <t>https://local.source/about-us</t>
